--- a/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/multi_document_paddle_vs_abbyy_errors_artifacts.xlsx
+++ b/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/multi_document_paddle_vs_abbyy_errors_artifacts.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overall Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Overall Summary" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -423,8 +423,8 @@
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
     <col width="60" customWidth="1" min="4" max="4"/>
-    <col width="31" customWidth="1" min="5" max="5"/>
-    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="33" customWidth="1" min="5" max="5"/>
+    <col width="32" customWidth="1" min="6" max="6"/>
     <col width="34" customWidth="1" min="7" max="7"/>
     <col width="33" customWidth="1" min="8" max="8"/>
     <col width="34" customWidth="1" min="9" max="9"/>
@@ -499,12 +499,12 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy</t>
         </is>
       </c>
       <c r="D2" s="1" t="n"/>
@@ -709,7 +709,7 @@
       </c>
       <c r="B7" s="1" t="inlineStr">
         <is>
-          <t>7874</t>
+          <t>7847</t>
         </is>
       </c>
       <c r="C7" s="1" t="inlineStr">
@@ -788,12 +788,12 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B9" s="1" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C9" s="1" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="E22" s="1" t="inlineStr">
         <is>
-          <t>paddle duplicate/tile overlap</t>
+          <t>paddle Possible duplicate lines</t>
         </is>
       </c>
       <c r="F22" s="1" t="inlineStr">
         <is>
-          <t>abbyy duplicate/tile overlap</t>
+          <t>abbyy Possible duplicate lines</t>
         </is>
       </c>
       <c r="G22" s="1" t="inlineStr">
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C23" s="1" t="inlineStr">
         <is>
-          <t>2668</t>
+          <t>2665</t>
         </is>
       </c>
       <c r="D23" s="1" t="inlineStr">
@@ -1468,7 +1468,7 @@
       </c>
       <c r="E23" s="1" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F23" s="1" t="inlineStr">
@@ -1592,7 +1592,7 @@
       </c>
       <c r="C24" s="1" t="inlineStr">
         <is>
-          <t>2573</t>
+          <t>2559</t>
         </is>
       </c>
       <c r="D24" s="1" t="inlineStr">
@@ -1602,7 +1602,7 @@
       </c>
       <c r="E24" s="1" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F24" s="1" t="inlineStr">
@@ -1726,7 +1726,7 @@
       </c>
       <c r="C25" s="1" t="inlineStr">
         <is>
-          <t>551</t>
+          <t>547</t>
         </is>
       </c>
       <c r="D25" s="1" t="inlineStr">
@@ -1736,7 +1736,7 @@
       </c>
       <c r="E25" s="1" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F25" s="1" t="inlineStr">
@@ -1860,7 +1860,7 @@
       </c>
       <c r="C26" s="1" t="inlineStr">
         <is>
-          <t>807</t>
+          <t>803</t>
         </is>
       </c>
       <c r="D26" s="1" t="inlineStr">
@@ -1870,7 +1870,7 @@
       </c>
       <c r="E26" s="1" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F26" s="1" t="inlineStr">
@@ -1994,7 +1994,7 @@
       </c>
       <c r="C27" s="1" t="inlineStr">
         <is>
-          <t>198</t>
+          <t>196</t>
         </is>
       </c>
       <c r="D27" s="1" t="inlineStr">
@@ -2004,7 +2004,7 @@
       </c>
       <c r="E27" s="1" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F27" s="1" t="inlineStr">
@@ -2480,12 +2480,12 @@
       </c>
       <c r="G32" s="1" t="inlineStr">
         <is>
-          <t>paddle duplicate/tile overlap</t>
+          <t>paddle Possible duplicate lines</t>
         </is>
       </c>
       <c r="H32" s="1" t="inlineStr">
         <is>
-          <t>abbyy duplicate/tile overlap</t>
+          <t>abbyy Possible duplicate lines</t>
         </is>
       </c>
       <c r="I32" s="1" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="C33" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\aeu.00037_19470820\aeu.00037_19470820.1.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\aeu.00037_19470820\aeu.00037_19470820.1.txt</t>
         </is>
       </c>
       <c r="D33" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\aeu.00037_19470820\aeu.00037_19470820.1.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\aeu.00037_19470820\aeu.00037_19470820.1.txt</t>
         </is>
       </c>
       <c r="E33" s="1" t="inlineStr">
@@ -2744,12 +2744,12 @@
       </c>
       <c r="C34" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\aeu.00037_19470820\aeu.00037_19470820.2.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\aeu.00037_19470820\aeu.00037_19470820.2.txt</t>
         </is>
       </c>
       <c r="D34" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\aeu.00037_19470820\aeu.00037_19470820.2.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\aeu.00037_19470820\aeu.00037_19470820.2.txt</t>
         </is>
       </c>
       <c r="E34" s="1" t="inlineStr">
@@ -2886,12 +2886,12 @@
       </c>
       <c r="C35" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\aeu.00037_19470820\aeu.00037_19470820.3.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\aeu.00037_19470820\aeu.00037_19470820.3.txt</t>
         </is>
       </c>
       <c r="D35" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\aeu.00037_19470820\aeu.00037_19470820.3.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\aeu.00037_19470820\aeu.00037_19470820.3.txt</t>
         </is>
       </c>
       <c r="E35" s="1" t="inlineStr">
@@ -3028,12 +3028,12 @@
       </c>
       <c r="C36" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\aeu.00037_19470820\aeu.00037_19470820.4.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\aeu.00037_19470820\aeu.00037_19470820.4.txt</t>
         </is>
       </c>
       <c r="D36" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\aeu.00037_19470820\aeu.00037_19470820.4.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\aeu.00037_19470820\aeu.00037_19470820.4.txt</t>
         </is>
       </c>
       <c r="E36" s="1" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="C37" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\aeu.00037_19470820\aeu.00037_19470820.5.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\aeu.00037_19470820\aeu.00037_19470820.5.txt</t>
         </is>
       </c>
       <c r="D37" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\aeu.00037_19470820\aeu.00037_19470820.5.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\aeu.00037_19470820\aeu.00037_19470820.5.txt</t>
         </is>
       </c>
       <c r="E37" s="1" t="inlineStr">
@@ -3312,17 +3312,17 @@
       </c>
       <c r="C38" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\aeu.00037_19470820\aeu.00037_19470820.6.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\aeu.00037_19470820\aeu.00037_19470820.6.txt</t>
         </is>
       </c>
       <c r="D38" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\aeu.00037_19470820\aeu.00037_19470820.6.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\aeu.00037_19470820\aeu.00037_19470820.6.txt</t>
         </is>
       </c>
       <c r="E38" s="1" t="inlineStr">
         <is>
-          <t>496</t>
+          <t>493</t>
         </is>
       </c>
       <c r="F38" s="1" t="inlineStr">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="G38" s="1" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H38" s="1" t="inlineStr">
@@ -3454,12 +3454,12 @@
       </c>
       <c r="C39" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\aeu.00037_19470820\aeu.00037_19470820.7.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\aeu.00037_19470820\aeu.00037_19470820.7.txt</t>
         </is>
       </c>
       <c r="D39" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\aeu.00037_19470820\aeu.00037_19470820.7.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\aeu.00037_19470820\aeu.00037_19470820.7.txt</t>
         </is>
       </c>
       <c r="E39" s="1" t="inlineStr">
@@ -3474,7 +3474,7 @@
       </c>
       <c r="G39" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H39" s="1" t="inlineStr">
@@ -3596,12 +3596,12 @@
       </c>
       <c r="C40" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\aeu.00037_19470820\aeu.00037_19470820.8.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\aeu.00037_19470820\aeu.00037_19470820.8.txt</t>
         </is>
       </c>
       <c r="D40" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\aeu.00037_19470820\aeu.00037_19470820.8.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\aeu.00037_19470820\aeu.00037_19470820.8.txt</t>
         </is>
       </c>
       <c r="E40" s="1" t="inlineStr">
@@ -3738,12 +3738,12 @@
       </c>
       <c r="C41" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.1.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.1.txt</t>
         </is>
       </c>
       <c r="D41" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0001.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0001.txt</t>
         </is>
       </c>
       <c r="E41" s="1" t="inlineStr">
@@ -3880,12 +3880,12 @@
       </c>
       <c r="C42" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.10.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.10.txt</t>
         </is>
       </c>
       <c r="D42" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0010.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0010.txt</t>
         </is>
       </c>
       <c r="E42" s="1" t="inlineStr">
@@ -4022,12 +4022,12 @@
       </c>
       <c r="C43" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.100.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.100.txt</t>
         </is>
       </c>
       <c r="D43" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0100.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0100.txt</t>
         </is>
       </c>
       <c r="E43" s="1" t="inlineStr">
@@ -4164,12 +4164,12 @@
       </c>
       <c r="C44" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.101.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.101.txt</t>
         </is>
       </c>
       <c r="D44" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0101.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0101.txt</t>
         </is>
       </c>
       <c r="E44" s="1" t="inlineStr">
@@ -4306,12 +4306,12 @@
       </c>
       <c r="C45" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.102.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.102.txt</t>
         </is>
       </c>
       <c r="D45" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0102.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0102.txt</t>
         </is>
       </c>
       <c r="E45" s="1" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="C46" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.103.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.103.txt</t>
         </is>
       </c>
       <c r="D46" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0103.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0103.txt</t>
         </is>
       </c>
       <c r="E46" s="1" t="inlineStr">
@@ -4590,12 +4590,12 @@
       </c>
       <c r="C47" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.104.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.104.txt</t>
         </is>
       </c>
       <c r="D47" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0104.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0104.txt</t>
         </is>
       </c>
       <c r="E47" s="1" t="inlineStr">
@@ -4732,12 +4732,12 @@
       </c>
       <c r="C48" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.105.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.105.txt</t>
         </is>
       </c>
       <c r="D48" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0105.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0105.txt</t>
         </is>
       </c>
       <c r="E48" s="1" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="C49" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.106.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.106.txt</t>
         </is>
       </c>
       <c r="D49" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0106.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0106.txt</t>
         </is>
       </c>
       <c r="E49" s="1" t="inlineStr">
@@ -5016,12 +5016,12 @@
       </c>
       <c r="C50" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.107.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.107.txt</t>
         </is>
       </c>
       <c r="D50" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0107.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0107.txt</t>
         </is>
       </c>
       <c r="E50" s="1" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="C51" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.108.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.108.txt</t>
         </is>
       </c>
       <c r="D51" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0108.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0108.txt</t>
         </is>
       </c>
       <c r="E51" s="1" t="inlineStr">
@@ -5300,12 +5300,12 @@
       </c>
       <c r="C52" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.109.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.109.txt</t>
         </is>
       </c>
       <c r="D52" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0109.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0109.txt</t>
         </is>
       </c>
       <c r="E52" s="1" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="C53" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.11.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.11.txt</t>
         </is>
       </c>
       <c r="D53" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0011.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0011.txt</t>
         </is>
       </c>
       <c r="E53" s="1" t="inlineStr">
@@ -5584,12 +5584,12 @@
       </c>
       <c r="C54" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.110.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.110.txt</t>
         </is>
       </c>
       <c r="D54" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0110.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0110.txt</t>
         </is>
       </c>
       <c r="E54" s="1" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="C55" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.111.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.111.txt</t>
         </is>
       </c>
       <c r="D55" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0111.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0111.txt</t>
         </is>
       </c>
       <c r="E55" s="1" t="inlineStr">
@@ -5868,17 +5868,17 @@
       </c>
       <c r="C56" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.112.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.112.txt</t>
         </is>
       </c>
       <c r="D56" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0112.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0112.txt</t>
         </is>
       </c>
       <c r="E56" s="1" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F56" s="1" t="inlineStr">
@@ -5888,7 +5888,7 @@
       </c>
       <c r="G56" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H56" s="1" t="inlineStr">
@@ -6010,12 +6010,12 @@
       </c>
       <c r="C57" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.113.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.113.txt</t>
         </is>
       </c>
       <c r="D57" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0113.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0113.txt</t>
         </is>
       </c>
       <c r="E57" s="1" t="inlineStr">
@@ -6152,17 +6152,17 @@
       </c>
       <c r="C58" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.114.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.114.txt</t>
         </is>
       </c>
       <c r="D58" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0114.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0114.txt</t>
         </is>
       </c>
       <c r="E58" s="1" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="F58" s="1" t="inlineStr">
@@ -6172,7 +6172,7 @@
       </c>
       <c r="G58" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H58" s="1" t="inlineStr">
@@ -6294,12 +6294,12 @@
       </c>
       <c r="C59" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.115.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.115.txt</t>
         </is>
       </c>
       <c r="D59" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0115.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0115.txt</t>
         </is>
       </c>
       <c r="E59" s="1" t="inlineStr">
@@ -6436,12 +6436,12 @@
       </c>
       <c r="C60" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.116.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.116.txt</t>
         </is>
       </c>
       <c r="D60" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0116.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0116.txt</t>
         </is>
       </c>
       <c r="E60" s="1" t="inlineStr">
@@ -6578,12 +6578,12 @@
       </c>
       <c r="C61" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.117.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.117.txt</t>
         </is>
       </c>
       <c r="D61" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0117.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0117.txt</t>
         </is>
       </c>
       <c r="E61" s="1" t="inlineStr">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="C62" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.118.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.118.txt</t>
         </is>
       </c>
       <c r="D62" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0118.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0118.txt</t>
         </is>
       </c>
       <c r="E62" s="1" t="inlineStr">
@@ -6862,12 +6862,12 @@
       </c>
       <c r="C63" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.119.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.119.txt</t>
         </is>
       </c>
       <c r="D63" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0119.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0119.txt</t>
         </is>
       </c>
       <c r="E63" s="1" t="inlineStr">
@@ -7004,12 +7004,12 @@
       </c>
       <c r="C64" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.12.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.12.txt</t>
         </is>
       </c>
       <c r="D64" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0012.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0012.txt</t>
         </is>
       </c>
       <c r="E64" s="1" t="inlineStr">
@@ -7146,12 +7146,12 @@
       </c>
       <c r="C65" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.120.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.120.txt</t>
         </is>
       </c>
       <c r="D65" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0120.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0120.txt</t>
         </is>
       </c>
       <c r="E65" s="1" t="inlineStr">
@@ -7288,12 +7288,12 @@
       </c>
       <c r="C66" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.121.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.121.txt</t>
         </is>
       </c>
       <c r="D66" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0121.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0121.txt</t>
         </is>
       </c>
       <c r="E66" s="1" t="inlineStr">
@@ -7430,12 +7430,12 @@
       </c>
       <c r="C67" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.122.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.122.txt</t>
         </is>
       </c>
       <c r="D67" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0122.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0122.txt</t>
         </is>
       </c>
       <c r="E67" s="1" t="inlineStr">
@@ -7572,12 +7572,12 @@
       </c>
       <c r="C68" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.123.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.123.txt</t>
         </is>
       </c>
       <c r="D68" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0123.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0123.txt</t>
         </is>
       </c>
       <c r="E68" s="1" t="inlineStr">
@@ -7714,12 +7714,12 @@
       </c>
       <c r="C69" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.124.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.124.txt</t>
         </is>
       </c>
       <c r="D69" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0124.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0124.txt</t>
         </is>
       </c>
       <c r="E69" s="1" t="inlineStr">
@@ -7856,12 +7856,12 @@
       </c>
       <c r="C70" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.125.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.125.txt</t>
         </is>
       </c>
       <c r="D70" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0125.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0125.txt</t>
         </is>
       </c>
       <c r="E70" s="1" t="inlineStr">
@@ -7998,12 +7998,12 @@
       </c>
       <c r="C71" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.126.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.126.txt</t>
         </is>
       </c>
       <c r="D71" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0126.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0126.txt</t>
         </is>
       </c>
       <c r="E71" s="1" t="inlineStr">
@@ -8140,12 +8140,12 @@
       </c>
       <c r="C72" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.127.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.127.txt</t>
         </is>
       </c>
       <c r="D72" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0127.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0127.txt</t>
         </is>
       </c>
       <c r="E72" s="1" t="inlineStr">
@@ -8282,12 +8282,12 @@
       </c>
       <c r="C73" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.128.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.128.txt</t>
         </is>
       </c>
       <c r="D73" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0128.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0128.txt</t>
         </is>
       </c>
       <c r="E73" s="1" t="inlineStr">
@@ -8424,12 +8424,12 @@
       </c>
       <c r="C74" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.129.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.129.txt</t>
         </is>
       </c>
       <c r="D74" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0129.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0129.txt</t>
         </is>
       </c>
       <c r="E74" s="1" t="inlineStr">
@@ -8566,12 +8566,12 @@
       </c>
       <c r="C75" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.13.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.13.txt</t>
         </is>
       </c>
       <c r="D75" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0013.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0013.txt</t>
         </is>
       </c>
       <c r="E75" s="1" t="inlineStr">
@@ -8708,12 +8708,12 @@
       </c>
       <c r="C76" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.130.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.130.txt</t>
         </is>
       </c>
       <c r="D76" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0130.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0130.txt</t>
         </is>
       </c>
       <c r="E76" s="1" t="inlineStr">
@@ -8850,12 +8850,12 @@
       </c>
       <c r="C77" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.131.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.131.txt</t>
         </is>
       </c>
       <c r="D77" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0131.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0131.txt</t>
         </is>
       </c>
       <c r="E77" s="1" t="inlineStr">
@@ -8992,12 +8992,12 @@
       </c>
       <c r="C78" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.132.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.132.txt</t>
         </is>
       </c>
       <c r="D78" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0132.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0132.txt</t>
         </is>
       </c>
       <c r="E78" s="1" t="inlineStr">
@@ -9134,12 +9134,12 @@
       </c>
       <c r="C79" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.133.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.133.txt</t>
         </is>
       </c>
       <c r="D79" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0133.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0133.txt</t>
         </is>
       </c>
       <c r="E79" s="1" t="inlineStr">
@@ -9276,12 +9276,12 @@
       </c>
       <c r="C80" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.134.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.134.txt</t>
         </is>
       </c>
       <c r="D80" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0134.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0134.txt</t>
         </is>
       </c>
       <c r="E80" s="1" t="inlineStr">
@@ -9418,27 +9418,27 @@
       </c>
       <c r="C81" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.135.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.135.txt</t>
         </is>
       </c>
       <c r="D81" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0135.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0135.txt</t>
         </is>
       </c>
       <c r="E81" s="1" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="F81" s="1" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="F81" s="1" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
       <c r="G81" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H81" s="1" t="inlineStr">
@@ -9560,12 +9560,12 @@
       </c>
       <c r="C82" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.136.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.136.txt</t>
         </is>
       </c>
       <c r="D82" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0136.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0136.txt</t>
         </is>
       </c>
       <c r="E82" s="1" t="inlineStr">
@@ -9702,12 +9702,12 @@
       </c>
       <c r="C83" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.137.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.137.txt</t>
         </is>
       </c>
       <c r="D83" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0137.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0137.txt</t>
         </is>
       </c>
       <c r="E83" s="1" t="inlineStr">
@@ -9844,12 +9844,12 @@
       </c>
       <c r="C84" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.138.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.138.txt</t>
         </is>
       </c>
       <c r="D84" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0138.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0138.txt</t>
         </is>
       </c>
       <c r="E84" s="1" t="inlineStr">
@@ -9986,12 +9986,12 @@
       </c>
       <c r="C85" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.139.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.139.txt</t>
         </is>
       </c>
       <c r="D85" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0139.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0139.txt</t>
         </is>
       </c>
       <c r="E85" s="1" t="inlineStr">
@@ -10128,12 +10128,12 @@
       </c>
       <c r="C86" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.14.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.14.txt</t>
         </is>
       </c>
       <c r="D86" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0014.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0014.txt</t>
         </is>
       </c>
       <c r="E86" s="1" t="inlineStr">
@@ -10270,12 +10270,12 @@
       </c>
       <c r="C87" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.140.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.140.txt</t>
         </is>
       </c>
       <c r="D87" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0140.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0140.txt</t>
         </is>
       </c>
       <c r="E87" s="1" t="inlineStr">
@@ -10412,12 +10412,12 @@
       </c>
       <c r="C88" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.141.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.141.txt</t>
         </is>
       </c>
       <c r="D88" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0141.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0141.txt</t>
         </is>
       </c>
       <c r="E88" s="1" t="inlineStr">
@@ -10554,12 +10554,12 @@
       </c>
       <c r="C89" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.142.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.142.txt</t>
         </is>
       </c>
       <c r="D89" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0142.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0142.txt</t>
         </is>
       </c>
       <c r="E89" s="1" t="inlineStr">
@@ -10696,12 +10696,12 @@
       </c>
       <c r="C90" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.143.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.143.txt</t>
         </is>
       </c>
       <c r="D90" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0143.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0143.txt</t>
         </is>
       </c>
       <c r="E90" s="1" t="inlineStr">
@@ -10838,17 +10838,17 @@
       </c>
       <c r="C91" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.144.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.144.txt</t>
         </is>
       </c>
       <c r="D91" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0144.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0144.txt</t>
         </is>
       </c>
       <c r="E91" s="1" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F91" s="1" t="inlineStr">
@@ -10858,7 +10858,7 @@
       </c>
       <c r="G91" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H91" s="1" t="inlineStr">
@@ -10980,12 +10980,12 @@
       </c>
       <c r="C92" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.145.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.145.txt</t>
         </is>
       </c>
       <c r="D92" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0145.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0145.txt</t>
         </is>
       </c>
       <c r="E92" s="1" t="inlineStr">
@@ -11122,12 +11122,12 @@
       </c>
       <c r="C93" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.146.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.146.txt</t>
         </is>
       </c>
       <c r="D93" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0146.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0146.txt</t>
         </is>
       </c>
       <c r="E93" s="1" t="inlineStr">
@@ -11264,12 +11264,12 @@
       </c>
       <c r="C94" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.147.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.147.txt</t>
         </is>
       </c>
       <c r="D94" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0147.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0147.txt</t>
         </is>
       </c>
       <c r="E94" s="1" t="inlineStr">
@@ -11406,12 +11406,12 @@
       </c>
       <c r="C95" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.148.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.148.txt</t>
         </is>
       </c>
       <c r="D95" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0148.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0148.txt</t>
         </is>
       </c>
       <c r="E95" s="1" t="inlineStr">
@@ -11548,12 +11548,12 @@
       </c>
       <c r="C96" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.149.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.149.txt</t>
         </is>
       </c>
       <c r="D96" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0149.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0149.txt</t>
         </is>
       </c>
       <c r="E96" s="1" t="inlineStr">
@@ -11690,17 +11690,17 @@
       </c>
       <c r="C97" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.15.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.15.txt</t>
         </is>
       </c>
       <c r="D97" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0015.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0015.txt</t>
         </is>
       </c>
       <c r="E97" s="1" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="F97" s="1" t="inlineStr">
@@ -11710,7 +11710,7 @@
       </c>
       <c r="G97" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H97" s="1" t="inlineStr">
@@ -11832,12 +11832,12 @@
       </c>
       <c r="C98" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.150.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.150.txt</t>
         </is>
       </c>
       <c r="D98" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0150.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0150.txt</t>
         </is>
       </c>
       <c r="E98" s="1" t="inlineStr">
@@ -11974,12 +11974,12 @@
       </c>
       <c r="C99" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.151.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.151.txt</t>
         </is>
       </c>
       <c r="D99" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0151.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0151.txt</t>
         </is>
       </c>
       <c r="E99" s="1" t="inlineStr">
@@ -12116,12 +12116,12 @@
       </c>
       <c r="C100" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.152.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.152.txt</t>
         </is>
       </c>
       <c r="D100" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0152.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0152.txt</t>
         </is>
       </c>
       <c r="E100" s="1" t="inlineStr">
@@ -12258,12 +12258,12 @@
       </c>
       <c r="C101" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.153.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.153.txt</t>
         </is>
       </c>
       <c r="D101" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0153.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0153.txt</t>
         </is>
       </c>
       <c r="E101" s="1" t="inlineStr">
@@ -12400,12 +12400,12 @@
       </c>
       <c r="C102" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.154.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.154.txt</t>
         </is>
       </c>
       <c r="D102" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0154.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0154.txt</t>
         </is>
       </c>
       <c r="E102" s="1" t="inlineStr">
@@ -12542,12 +12542,12 @@
       </c>
       <c r="C103" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.155.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.155.txt</t>
         </is>
       </c>
       <c r="D103" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0155.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0155.txt</t>
         </is>
       </c>
       <c r="E103" s="1" t="inlineStr">
@@ -12684,12 +12684,12 @@
       </c>
       <c r="C104" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.156.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.156.txt</t>
         </is>
       </c>
       <c r="D104" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0156.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0156.txt</t>
         </is>
       </c>
       <c r="E104" s="1" t="inlineStr">
@@ -12826,12 +12826,12 @@
       </c>
       <c r="C105" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.157.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.157.txt</t>
         </is>
       </c>
       <c r="D105" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0157.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0157.txt</t>
         </is>
       </c>
       <c r="E105" s="1" t="inlineStr">
@@ -12968,12 +12968,12 @@
       </c>
       <c r="C106" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.158.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.158.txt</t>
         </is>
       </c>
       <c r="D106" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0158.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0158.txt</t>
         </is>
       </c>
       <c r="E106" s="1" t="inlineStr">
@@ -13110,12 +13110,12 @@
       </c>
       <c r="C107" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.159.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.159.txt</t>
         </is>
       </c>
       <c r="D107" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0159.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0159.txt</t>
         </is>
       </c>
       <c r="E107" s="1" t="inlineStr">
@@ -13252,12 +13252,12 @@
       </c>
       <c r="C108" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.16.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.16.txt</t>
         </is>
       </c>
       <c r="D108" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0016.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0016.txt</t>
         </is>
       </c>
       <c r="E108" s="1" t="inlineStr">
@@ -13394,12 +13394,12 @@
       </c>
       <c r="C109" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.160.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.160.txt</t>
         </is>
       </c>
       <c r="D109" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0160.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0160.txt</t>
         </is>
       </c>
       <c r="E109" s="1" t="inlineStr">
@@ -13536,12 +13536,12 @@
       </c>
       <c r="C110" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.161.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.161.txt</t>
         </is>
       </c>
       <c r="D110" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0161.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0161.txt</t>
         </is>
       </c>
       <c r="E110" s="1" t="inlineStr">
@@ -13678,12 +13678,12 @@
       </c>
       <c r="C111" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.162.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.162.txt</t>
         </is>
       </c>
       <c r="D111" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0162.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0162.txt</t>
         </is>
       </c>
       <c r="E111" s="1" t="inlineStr">
@@ -13820,12 +13820,12 @@
       </c>
       <c r="C112" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.163.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.163.txt</t>
         </is>
       </c>
       <c r="D112" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0163.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0163.txt</t>
         </is>
       </c>
       <c r="E112" s="1" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="C113" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.164.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.164.txt</t>
         </is>
       </c>
       <c r="D113" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0164.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0164.txt</t>
         </is>
       </c>
       <c r="E113" s="1" t="inlineStr">
@@ -14104,12 +14104,12 @@
       </c>
       <c r="C114" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.165.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.165.txt</t>
         </is>
       </c>
       <c r="D114" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0165.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0165.txt</t>
         </is>
       </c>
       <c r="E114" s="1" t="inlineStr">
@@ -14246,12 +14246,12 @@
       </c>
       <c r="C115" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.166.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.166.txt</t>
         </is>
       </c>
       <c r="D115" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0166.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0166.txt</t>
         </is>
       </c>
       <c r="E115" s="1" t="inlineStr">
@@ -14388,12 +14388,12 @@
       </c>
       <c r="C116" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.167.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.167.txt</t>
         </is>
       </c>
       <c r="D116" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0167.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0167.txt</t>
         </is>
       </c>
       <c r="E116" s="1" t="inlineStr">
@@ -14530,12 +14530,12 @@
       </c>
       <c r="C117" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.168.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.168.txt</t>
         </is>
       </c>
       <c r="D117" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0168.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0168.txt</t>
         </is>
       </c>
       <c r="E117" s="1" t="inlineStr">
@@ -14672,12 +14672,12 @@
       </c>
       <c r="C118" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.169.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.169.txt</t>
         </is>
       </c>
       <c r="D118" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0169.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0169.txt</t>
         </is>
       </c>
       <c r="E118" s="1" t="inlineStr">
@@ -14814,12 +14814,12 @@
       </c>
       <c r="C119" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.17.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.17.txt</t>
         </is>
       </c>
       <c r="D119" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0017.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0017.txt</t>
         </is>
       </c>
       <c r="E119" s="1" t="inlineStr">
@@ -14956,12 +14956,12 @@
       </c>
       <c r="C120" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.170.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.170.txt</t>
         </is>
       </c>
       <c r="D120" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0170.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0170.txt</t>
         </is>
       </c>
       <c r="E120" s="1" t="inlineStr">
@@ -15098,12 +15098,12 @@
       </c>
       <c r="C121" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.171.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.171.txt</t>
         </is>
       </c>
       <c r="D121" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0171.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0171.txt</t>
         </is>
       </c>
       <c r="E121" s="1" t="inlineStr">
@@ -15240,12 +15240,12 @@
       </c>
       <c r="C122" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.172.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.172.txt</t>
         </is>
       </c>
       <c r="D122" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0172.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0172.txt</t>
         </is>
       </c>
       <c r="E122" s="1" t="inlineStr">
@@ -15382,12 +15382,12 @@
       </c>
       <c r="C123" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.173.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.173.txt</t>
         </is>
       </c>
       <c r="D123" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0173.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0173.txt</t>
         </is>
       </c>
       <c r="E123" s="1" t="inlineStr">
@@ -15524,12 +15524,12 @@
       </c>
       <c r="C124" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.174.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.174.txt</t>
         </is>
       </c>
       <c r="D124" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0174.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0174.txt</t>
         </is>
       </c>
       <c r="E124" s="1" t="inlineStr">
@@ -15666,17 +15666,17 @@
       </c>
       <c r="C125" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.175.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.175.txt</t>
         </is>
       </c>
       <c r="D125" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0175.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0175.txt</t>
         </is>
       </c>
       <c r="E125" s="1" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="F125" s="1" t="inlineStr">
@@ -15686,7 +15686,7 @@
       </c>
       <c r="G125" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H125" s="1" t="inlineStr">
@@ -15808,12 +15808,12 @@
       </c>
       <c r="C126" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.176.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.176.txt</t>
         </is>
       </c>
       <c r="D126" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0176.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0176.txt</t>
         </is>
       </c>
       <c r="E126" s="1" t="inlineStr">
@@ -15950,12 +15950,12 @@
       </c>
       <c r="C127" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.177.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.177.txt</t>
         </is>
       </c>
       <c r="D127" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0177.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0177.txt</t>
         </is>
       </c>
       <c r="E127" s="1" t="inlineStr">
@@ -16092,12 +16092,12 @@
       </c>
       <c r="C128" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.18.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.18.txt</t>
         </is>
       </c>
       <c r="D128" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0018.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0018.txt</t>
         </is>
       </c>
       <c r="E128" s="1" t="inlineStr">
@@ -16234,12 +16234,12 @@
       </c>
       <c r="C129" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.19.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.19.txt</t>
         </is>
       </c>
       <c r="D129" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0019.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0019.txt</t>
         </is>
       </c>
       <c r="E129" s="1" t="inlineStr">
@@ -16376,12 +16376,12 @@
       </c>
       <c r="C130" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.2.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.2.txt</t>
         </is>
       </c>
       <c r="D130" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0002.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0002.txt</t>
         </is>
       </c>
       <c r="E130" s="1" t="inlineStr">
@@ -16518,12 +16518,12 @@
       </c>
       <c r="C131" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.20.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.20.txt</t>
         </is>
       </c>
       <c r="D131" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0020.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0020.txt</t>
         </is>
       </c>
       <c r="E131" s="1" t="inlineStr">
@@ -16660,12 +16660,12 @@
       </c>
       <c r="C132" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.21.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.21.txt</t>
         </is>
       </c>
       <c r="D132" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0021.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0021.txt</t>
         </is>
       </c>
       <c r="E132" s="1" t="inlineStr">
@@ -16802,12 +16802,12 @@
       </c>
       <c r="C133" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.22.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.22.txt</t>
         </is>
       </c>
       <c r="D133" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0022.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0022.txt</t>
         </is>
       </c>
       <c r="E133" s="1" t="inlineStr">
@@ -16944,12 +16944,12 @@
       </c>
       <c r="C134" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.23.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.23.txt</t>
         </is>
       </c>
       <c r="D134" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0023.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0023.txt</t>
         </is>
       </c>
       <c r="E134" s="1" t="inlineStr">
@@ -17086,12 +17086,12 @@
       </c>
       <c r="C135" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.24.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.24.txt</t>
         </is>
       </c>
       <c r="D135" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0024.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0024.txt</t>
         </is>
       </c>
       <c r="E135" s="1" t="inlineStr">
@@ -17228,12 +17228,12 @@
       </c>
       <c r="C136" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.25.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.25.txt</t>
         </is>
       </c>
       <c r="D136" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0025.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0025.txt</t>
         </is>
       </c>
       <c r="E136" s="1" t="inlineStr">
@@ -17370,12 +17370,12 @@
       </c>
       <c r="C137" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.26.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.26.txt</t>
         </is>
       </c>
       <c r="D137" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0026.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0026.txt</t>
         </is>
       </c>
       <c r="E137" s="1" t="inlineStr">
@@ -17512,12 +17512,12 @@
       </c>
       <c r="C138" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.27.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.27.txt</t>
         </is>
       </c>
       <c r="D138" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0027.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0027.txt</t>
         </is>
       </c>
       <c r="E138" s="1" t="inlineStr">
@@ -17654,17 +17654,17 @@
       </c>
       <c r="C139" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.28.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.28.txt</t>
         </is>
       </c>
       <c r="D139" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0028.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0028.txt</t>
         </is>
       </c>
       <c r="E139" s="1" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F139" s="1" t="inlineStr">
@@ -17674,7 +17674,7 @@
       </c>
       <c r="G139" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H139" s="1" t="inlineStr">
@@ -17796,17 +17796,17 @@
       </c>
       <c r="C140" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.29.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.29.txt</t>
         </is>
       </c>
       <c r="D140" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0029.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0029.txt</t>
         </is>
       </c>
       <c r="E140" s="1" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="F140" s="1" t="inlineStr">
@@ -17816,7 +17816,7 @@
       </c>
       <c r="G140" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H140" s="1" t="inlineStr">
@@ -17938,17 +17938,17 @@
       </c>
       <c r="C141" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.3.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.3.txt</t>
         </is>
       </c>
       <c r="D141" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0003.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0003.txt</t>
         </is>
       </c>
       <c r="E141" s="1" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>75</t>
         </is>
       </c>
       <c r="F141" s="1" t="inlineStr">
@@ -17958,7 +17958,7 @@
       </c>
       <c r="G141" s="1" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H141" s="1" t="inlineStr">
@@ -18080,12 +18080,12 @@
       </c>
       <c r="C142" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.30.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.30.txt</t>
         </is>
       </c>
       <c r="D142" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0030.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0030.txt</t>
         </is>
       </c>
       <c r="E142" s="1" t="inlineStr">
@@ -18222,12 +18222,12 @@
       </c>
       <c r="C143" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.31.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.31.txt</t>
         </is>
       </c>
       <c r="D143" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0031.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0031.txt</t>
         </is>
       </c>
       <c r="E143" s="1" t="inlineStr">
@@ -18364,12 +18364,12 @@
       </c>
       <c r="C144" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.32.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.32.txt</t>
         </is>
       </c>
       <c r="D144" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0032.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0032.txt</t>
         </is>
       </c>
       <c r="E144" s="1" t="inlineStr">
@@ -18506,12 +18506,12 @@
       </c>
       <c r="C145" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.33.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.33.txt</t>
         </is>
       </c>
       <c r="D145" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0033.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0033.txt</t>
         </is>
       </c>
       <c r="E145" s="1" t="inlineStr">
@@ -18648,12 +18648,12 @@
       </c>
       <c r="C146" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.34.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.34.txt</t>
         </is>
       </c>
       <c r="D146" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0034.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0034.txt</t>
         </is>
       </c>
       <c r="E146" s="1" t="inlineStr">
@@ -18790,12 +18790,12 @@
       </c>
       <c r="C147" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.35.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.35.txt</t>
         </is>
       </c>
       <c r="D147" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0035.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0035.txt</t>
         </is>
       </c>
       <c r="E147" s="1" t="inlineStr">
@@ -18932,12 +18932,12 @@
       </c>
       <c r="C148" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.36.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.36.txt</t>
         </is>
       </c>
       <c r="D148" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0036.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0036.txt</t>
         </is>
       </c>
       <c r="E148" s="1" t="inlineStr">
@@ -19074,12 +19074,12 @@
       </c>
       <c r="C149" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.37.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.37.txt</t>
         </is>
       </c>
       <c r="D149" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0037.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0037.txt</t>
         </is>
       </c>
       <c r="E149" s="1" t="inlineStr">
@@ -19216,12 +19216,12 @@
       </c>
       <c r="C150" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.38.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.38.txt</t>
         </is>
       </c>
       <c r="D150" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0038.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0038.txt</t>
         </is>
       </c>
       <c r="E150" s="1" t="inlineStr">
@@ -19358,12 +19358,12 @@
       </c>
       <c r="C151" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.39.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.39.txt</t>
         </is>
       </c>
       <c r="D151" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0039.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0039.txt</t>
         </is>
       </c>
       <c r="E151" s="1" t="inlineStr">
@@ -19500,12 +19500,12 @@
       </c>
       <c r="C152" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.4.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.4.txt</t>
         </is>
       </c>
       <c r="D152" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0004.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0004.txt</t>
         </is>
       </c>
       <c r="E152" s="1" t="inlineStr">
@@ -19642,12 +19642,12 @@
       </c>
       <c r="C153" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.40.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.40.txt</t>
         </is>
       </c>
       <c r="D153" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0040.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0040.txt</t>
         </is>
       </c>
       <c r="E153" s="1" t="inlineStr">
@@ -19784,12 +19784,12 @@
       </c>
       <c r="C154" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.41.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.41.txt</t>
         </is>
       </c>
       <c r="D154" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0041.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0041.txt</t>
         </is>
       </c>
       <c r="E154" s="1" t="inlineStr">
@@ -19926,12 +19926,12 @@
       </c>
       <c r="C155" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.42.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.42.txt</t>
         </is>
       </c>
       <c r="D155" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0042.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0042.txt</t>
         </is>
       </c>
       <c r="E155" s="1" t="inlineStr">
@@ -20068,12 +20068,12 @@
       </c>
       <c r="C156" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.43.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.43.txt</t>
         </is>
       </c>
       <c r="D156" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0043.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0043.txt</t>
         </is>
       </c>
       <c r="E156" s="1" t="inlineStr">
@@ -20210,12 +20210,12 @@
       </c>
       <c r="C157" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.44.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.44.txt</t>
         </is>
       </c>
       <c r="D157" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0044.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0044.txt</t>
         </is>
       </c>
       <c r="E157" s="1" t="inlineStr">
@@ -20352,12 +20352,12 @@
       </c>
       <c r="C158" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.45.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.45.txt</t>
         </is>
       </c>
       <c r="D158" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0045.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0045.txt</t>
         </is>
       </c>
       <c r="E158" s="1" t="inlineStr">
@@ -20494,12 +20494,12 @@
       </c>
       <c r="C159" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.46.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.46.txt</t>
         </is>
       </c>
       <c r="D159" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0046.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0046.txt</t>
         </is>
       </c>
       <c r="E159" s="1" t="inlineStr">
@@ -20636,12 +20636,12 @@
       </c>
       <c r="C160" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.47.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.47.txt</t>
         </is>
       </c>
       <c r="D160" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0047.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0047.txt</t>
         </is>
       </c>
       <c r="E160" s="1" t="inlineStr">
@@ -20778,12 +20778,12 @@
       </c>
       <c r="C161" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.48.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.48.txt</t>
         </is>
       </c>
       <c r="D161" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0048.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0048.txt</t>
         </is>
       </c>
       <c r="E161" s="1" t="inlineStr">
@@ -20920,12 +20920,12 @@
       </c>
       <c r="C162" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.49.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.49.txt</t>
         </is>
       </c>
       <c r="D162" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0049.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0049.txt</t>
         </is>
       </c>
       <c r="E162" s="1" t="inlineStr">
@@ -21062,12 +21062,12 @@
       </c>
       <c r="C163" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.5.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.5.txt</t>
         </is>
       </c>
       <c r="D163" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0005.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0005.txt</t>
         </is>
       </c>
       <c r="E163" s="1" t="inlineStr">
@@ -21204,12 +21204,12 @@
       </c>
       <c r="C164" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.50.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.50.txt</t>
         </is>
       </c>
       <c r="D164" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0050.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0050.txt</t>
         </is>
       </c>
       <c r="E164" s="1" t="inlineStr">
@@ -21346,12 +21346,12 @@
       </c>
       <c r="C165" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.51.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.51.txt</t>
         </is>
       </c>
       <c r="D165" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0051.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0051.txt</t>
         </is>
       </c>
       <c r="E165" s="1" t="inlineStr">
@@ -21488,12 +21488,12 @@
       </c>
       <c r="C166" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.52.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.52.txt</t>
         </is>
       </c>
       <c r="D166" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0052.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0052.txt</t>
         </is>
       </c>
       <c r="E166" s="1" t="inlineStr">
@@ -21630,12 +21630,12 @@
       </c>
       <c r="C167" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.53.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.53.txt</t>
         </is>
       </c>
       <c r="D167" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0053.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0053.txt</t>
         </is>
       </c>
       <c r="E167" s="1" t="inlineStr">
@@ -21772,12 +21772,12 @@
       </c>
       <c r="C168" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.54.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.54.txt</t>
         </is>
       </c>
       <c r="D168" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0054.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0054.txt</t>
         </is>
       </c>
       <c r="E168" s="1" t="inlineStr">
@@ -21914,12 +21914,12 @@
       </c>
       <c r="C169" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.55.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.55.txt</t>
         </is>
       </c>
       <c r="D169" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0055.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0055.txt</t>
         </is>
       </c>
       <c r="E169" s="1" t="inlineStr">
@@ -22056,12 +22056,12 @@
       </c>
       <c r="C170" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.56.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.56.txt</t>
         </is>
       </c>
       <c r="D170" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0056.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0056.txt</t>
         </is>
       </c>
       <c r="E170" s="1" t="inlineStr">
@@ -22198,17 +22198,17 @@
       </c>
       <c r="C171" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.57.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.57.txt</t>
         </is>
       </c>
       <c r="D171" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0057.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0057.txt</t>
         </is>
       </c>
       <c r="E171" s="1" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="F171" s="1" t="inlineStr">
@@ -22218,7 +22218,7 @@
       </c>
       <c r="G171" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H171" s="1" t="inlineStr">
@@ -22340,12 +22340,12 @@
       </c>
       <c r="C172" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.58.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.58.txt</t>
         </is>
       </c>
       <c r="D172" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0058.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0058.txt</t>
         </is>
       </c>
       <c r="E172" s="1" t="inlineStr">
@@ -22482,12 +22482,12 @@
       </c>
       <c r="C173" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.59.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.59.txt</t>
         </is>
       </c>
       <c r="D173" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0059.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0059.txt</t>
         </is>
       </c>
       <c r="E173" s="1" t="inlineStr">
@@ -22624,12 +22624,12 @@
       </c>
       <c r="C174" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.6.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.6.txt</t>
         </is>
       </c>
       <c r="D174" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0006.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0006.txt</t>
         </is>
       </c>
       <c r="E174" s="1" t="inlineStr">
@@ -22766,12 +22766,12 @@
       </c>
       <c r="C175" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.60.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.60.txt</t>
         </is>
       </c>
       <c r="D175" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0060.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0060.txt</t>
         </is>
       </c>
       <c r="E175" s="1" t="inlineStr">
@@ -22908,12 +22908,12 @@
       </c>
       <c r="C176" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.61.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.61.txt</t>
         </is>
       </c>
       <c r="D176" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0061.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0061.txt</t>
         </is>
       </c>
       <c r="E176" s="1" t="inlineStr">
@@ -23050,12 +23050,12 @@
       </c>
       <c r="C177" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.62.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.62.txt</t>
         </is>
       </c>
       <c r="D177" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0062.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0062.txt</t>
         </is>
       </c>
       <c r="E177" s="1" t="inlineStr">
@@ -23192,12 +23192,12 @@
       </c>
       <c r="C178" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.63.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.63.txt</t>
         </is>
       </c>
       <c r="D178" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0063.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0063.txt</t>
         </is>
       </c>
       <c r="E178" s="1" t="inlineStr">
@@ -23334,12 +23334,12 @@
       </c>
       <c r="C179" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.64.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.64.txt</t>
         </is>
       </c>
       <c r="D179" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0064.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0064.txt</t>
         </is>
       </c>
       <c r="E179" s="1" t="inlineStr">
@@ -23476,12 +23476,12 @@
       </c>
       <c r="C180" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.65.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.65.txt</t>
         </is>
       </c>
       <c r="D180" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0065.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0065.txt</t>
         </is>
       </c>
       <c r="E180" s="1" t="inlineStr">
@@ -23618,12 +23618,12 @@
       </c>
       <c r="C181" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.66.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.66.txt</t>
         </is>
       </c>
       <c r="D181" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0066.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0066.txt</t>
         </is>
       </c>
       <c r="E181" s="1" t="inlineStr">
@@ -23760,12 +23760,12 @@
       </c>
       <c r="C182" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.67.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.67.txt</t>
         </is>
       </c>
       <c r="D182" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0067.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0067.txt</t>
         </is>
       </c>
       <c r="E182" s="1" t="inlineStr">
@@ -23902,12 +23902,12 @@
       </c>
       <c r="C183" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.68.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.68.txt</t>
         </is>
       </c>
       <c r="D183" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0068.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0068.txt</t>
         </is>
       </c>
       <c r="E183" s="1" t="inlineStr">
@@ -24044,12 +24044,12 @@
       </c>
       <c r="C184" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.69.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.69.txt</t>
         </is>
       </c>
       <c r="D184" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0069.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0069.txt</t>
         </is>
       </c>
       <c r="E184" s="1" t="inlineStr">
@@ -24186,12 +24186,12 @@
       </c>
       <c r="C185" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.7.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.7.txt</t>
         </is>
       </c>
       <c r="D185" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0007.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0007.txt</t>
         </is>
       </c>
       <c r="E185" s="1" t="inlineStr">
@@ -24328,12 +24328,12 @@
       </c>
       <c r="C186" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.70.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.70.txt</t>
         </is>
       </c>
       <c r="D186" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0070.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0070.txt</t>
         </is>
       </c>
       <c r="E186" s="1" t="inlineStr">
@@ -24470,12 +24470,12 @@
       </c>
       <c r="C187" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.71.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.71.txt</t>
         </is>
       </c>
       <c r="D187" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0071.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0071.txt</t>
         </is>
       </c>
       <c r="E187" s="1" t="inlineStr">
@@ -24612,12 +24612,12 @@
       </c>
       <c r="C188" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.72.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.72.txt</t>
         </is>
       </c>
       <c r="D188" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0072.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0072.txt</t>
         </is>
       </c>
       <c r="E188" s="1" t="inlineStr">
@@ -24754,12 +24754,12 @@
       </c>
       <c r="C189" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.73.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.73.txt</t>
         </is>
       </c>
       <c r="D189" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0073.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0073.txt</t>
         </is>
       </c>
       <c r="E189" s="1" t="inlineStr">
@@ -24896,12 +24896,12 @@
       </c>
       <c r="C190" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.74.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.74.txt</t>
         </is>
       </c>
       <c r="D190" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0074.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0074.txt</t>
         </is>
       </c>
       <c r="E190" s="1" t="inlineStr">
@@ -25038,12 +25038,12 @@
       </c>
       <c r="C191" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.75.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.75.txt</t>
         </is>
       </c>
       <c r="D191" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0075.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0075.txt</t>
         </is>
       </c>
       <c r="E191" s="1" t="inlineStr">
@@ -25180,12 +25180,12 @@
       </c>
       <c r="C192" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.76.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.76.txt</t>
         </is>
       </c>
       <c r="D192" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0076.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0076.txt</t>
         </is>
       </c>
       <c r="E192" s="1" t="inlineStr">
@@ -25322,12 +25322,12 @@
       </c>
       <c r="C193" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.77.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.77.txt</t>
         </is>
       </c>
       <c r="D193" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0077.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0077.txt</t>
         </is>
       </c>
       <c r="E193" s="1" t="inlineStr">
@@ -25464,12 +25464,12 @@
       </c>
       <c r="C194" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.78.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.78.txt</t>
         </is>
       </c>
       <c r="D194" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0078.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0078.txt</t>
         </is>
       </c>
       <c r="E194" s="1" t="inlineStr">
@@ -25606,12 +25606,12 @@
       </c>
       <c r="C195" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.79.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.79.txt</t>
         </is>
       </c>
       <c r="D195" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0079.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0079.txt</t>
         </is>
       </c>
       <c r="E195" s="1" t="inlineStr">
@@ -25748,17 +25748,17 @@
       </c>
       <c r="C196" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.8.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.8.txt</t>
         </is>
       </c>
       <c r="D196" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0008.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0008.txt</t>
         </is>
       </c>
       <c r="E196" s="1" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="F196" s="1" t="inlineStr">
@@ -25768,7 +25768,7 @@
       </c>
       <c r="G196" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H196" s="1" t="inlineStr">
@@ -25890,12 +25890,12 @@
       </c>
       <c r="C197" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.80.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.80.txt</t>
         </is>
       </c>
       <c r="D197" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0080.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0080.txt</t>
         </is>
       </c>
       <c r="E197" s="1" t="inlineStr">
@@ -26032,12 +26032,12 @@
       </c>
       <c r="C198" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.81.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.81.txt</t>
         </is>
       </c>
       <c r="D198" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0081.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0081.txt</t>
         </is>
       </c>
       <c r="E198" s="1" t="inlineStr">
@@ -26174,12 +26174,12 @@
       </c>
       <c r="C199" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.82.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.82.txt</t>
         </is>
       </c>
       <c r="D199" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0082.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0082.txt</t>
         </is>
       </c>
       <c r="E199" s="1" t="inlineStr">
@@ -26316,12 +26316,12 @@
       </c>
       <c r="C200" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.83.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.83.txt</t>
         </is>
       </c>
       <c r="D200" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0083.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0083.txt</t>
         </is>
       </c>
       <c r="E200" s="1" t="inlineStr">
@@ -26458,12 +26458,12 @@
       </c>
       <c r="C201" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.84.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.84.txt</t>
         </is>
       </c>
       <c r="D201" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0084.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0084.txt</t>
         </is>
       </c>
       <c r="E201" s="1" t="inlineStr">
@@ -26600,12 +26600,12 @@
       </c>
       <c r="C202" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.85.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.85.txt</t>
         </is>
       </c>
       <c r="D202" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0085.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0085.txt</t>
         </is>
       </c>
       <c r="E202" s="1" t="inlineStr">
@@ -26742,17 +26742,17 @@
       </c>
       <c r="C203" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.86.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.86.txt</t>
         </is>
       </c>
       <c r="D203" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0086.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0086.txt</t>
         </is>
       </c>
       <c r="E203" s="1" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F203" s="1" t="inlineStr">
@@ -26762,7 +26762,7 @@
       </c>
       <c r="G203" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H203" s="1" t="inlineStr">
@@ -26884,12 +26884,12 @@
       </c>
       <c r="C204" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.87.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.87.txt</t>
         </is>
       </c>
       <c r="D204" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0087.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0087.txt</t>
         </is>
       </c>
       <c r="E204" s="1" t="inlineStr">
@@ -27026,12 +27026,12 @@
       </c>
       <c r="C205" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.88.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.88.txt</t>
         </is>
       </c>
       <c r="D205" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0088.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0088.txt</t>
         </is>
       </c>
       <c r="E205" s="1" t="inlineStr">
@@ -27168,12 +27168,12 @@
       </c>
       <c r="C206" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.89.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.89.txt</t>
         </is>
       </c>
       <c r="D206" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0089.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0089.txt</t>
         </is>
       </c>
       <c r="E206" s="1" t="inlineStr">
@@ -27310,12 +27310,12 @@
       </c>
       <c r="C207" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.9.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.9.txt</t>
         </is>
       </c>
       <c r="D207" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0009.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0009.txt</t>
         </is>
       </c>
       <c r="E207" s="1" t="inlineStr">
@@ -27452,12 +27452,12 @@
       </c>
       <c r="C208" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.90.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.90.txt</t>
         </is>
       </c>
       <c r="D208" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0090.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0090.txt</t>
         </is>
       </c>
       <c r="E208" s="1" t="inlineStr">
@@ -27594,12 +27594,12 @@
       </c>
       <c r="C209" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.91.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.91.txt</t>
         </is>
       </c>
       <c r="D209" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0091.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0091.txt</t>
         </is>
       </c>
       <c r="E209" s="1" t="inlineStr">
@@ -27736,12 +27736,12 @@
       </c>
       <c r="C210" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.92.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.92.txt</t>
         </is>
       </c>
       <c r="D210" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0092.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0092.txt</t>
         </is>
       </c>
       <c r="E210" s="1" t="inlineStr">
@@ -27878,12 +27878,12 @@
       </c>
       <c r="C211" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.93.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.93.txt</t>
         </is>
       </c>
       <c r="D211" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0093.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0093.txt</t>
         </is>
       </c>
       <c r="E211" s="1" t="inlineStr">
@@ -28020,12 +28020,12 @@
       </c>
       <c r="C212" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.94.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.94.txt</t>
         </is>
       </c>
       <c r="D212" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0094.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0094.txt</t>
         </is>
       </c>
       <c r="E212" s="1" t="inlineStr">
@@ -28162,12 +28162,12 @@
       </c>
       <c r="C213" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.95.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.95.txt</t>
         </is>
       </c>
       <c r="D213" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0095.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0095.txt</t>
         </is>
       </c>
       <c r="E213" s="1" t="inlineStr">
@@ -28304,12 +28304,12 @@
       </c>
       <c r="C214" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.96.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.96.txt</t>
         </is>
       </c>
       <c r="D214" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0096.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0096.txt</t>
         </is>
       </c>
       <c r="E214" s="1" t="inlineStr">
@@ -28446,12 +28446,12 @@
       </c>
       <c r="C215" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.97.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.97.txt</t>
         </is>
       </c>
       <c r="D215" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0097.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0097.txt</t>
         </is>
       </c>
       <c r="E215" s="1" t="inlineStr">
@@ -28588,12 +28588,12 @@
       </c>
       <c r="C216" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.98.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.98.txt</t>
         </is>
       </c>
       <c r="D216" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0098.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0098.txt</t>
         </is>
       </c>
       <c r="E216" s="1" t="inlineStr">
@@ -28730,12 +28730,12 @@
       </c>
       <c r="C217" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.99.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.99.txt</t>
         </is>
       </c>
       <c r="D217" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0099.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0099.txt</t>
         </is>
       </c>
       <c r="E217" s="1" t="inlineStr">
@@ -28872,17 +28872,17 @@
       </c>
       <c r="C218" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.N_00126_19130805\oocihm.N_00126_19130805.1.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.N_00126_19130805\oocihm.N_00126_19130805.1.txt</t>
         </is>
       </c>
       <c r="D218" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.N_00126_19130805\oocihm.N_00126_19130805.1.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.N_00126_19130805\oocihm.N_00126_19130805.1.txt</t>
         </is>
       </c>
       <c r="E218" s="1" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>29</t>
         </is>
       </c>
       <c r="F218" s="1" t="inlineStr">
@@ -28892,7 +28892,7 @@
       </c>
       <c r="G218" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H218" s="1" t="inlineStr">
@@ -29014,12 +29014,12 @@
       </c>
       <c r="C219" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.N_00126_19130805\oocihm.N_00126_19130805.2.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.N_00126_19130805\oocihm.N_00126_19130805.2.txt</t>
         </is>
       </c>
       <c r="D219" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.N_00126_19130805\oocihm.N_00126_19130805.2.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.N_00126_19130805\oocihm.N_00126_19130805.2.txt</t>
         </is>
       </c>
       <c r="E219" s="1" t="inlineStr">
@@ -29156,17 +29156,17 @@
       </c>
       <c r="C220" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.N_00126_19130805\oocihm.N_00126_19130805.3.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.N_00126_19130805\oocihm.N_00126_19130805.3.txt</t>
         </is>
       </c>
       <c r="D220" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.N_00126_19130805\oocihm.N_00126_19130805.3.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.N_00126_19130805\oocihm.N_00126_19130805.3.txt</t>
         </is>
       </c>
       <c r="E220" s="1" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>47</t>
         </is>
       </c>
       <c r="F220" s="1" t="inlineStr">
@@ -29176,7 +29176,7 @@
       </c>
       <c r="G220" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H220" s="1" t="inlineStr">
@@ -29298,12 +29298,12 @@
       </c>
       <c r="C221" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.N_00126_19130805\oocihm.N_00126_19130805.4.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.N_00126_19130805\oocihm.N_00126_19130805.4.txt</t>
         </is>
       </c>
       <c r="D221" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.N_00126_19130805\oocihm.N_00126_19130805.4.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.N_00126_19130805\oocihm.N_00126_19130805.4.txt</t>
         </is>
       </c>
       <c r="E221" s="1" t="inlineStr">
@@ -29440,17 +29440,17 @@
       </c>
       <c r="C222" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.N_00126_19130805\oocihm.N_00126_19130805.5.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.N_00126_19130805\oocihm.N_00126_19130805.5.txt</t>
         </is>
       </c>
       <c r="D222" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.N_00126_19130805\oocihm.N_00126_19130805.5.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.N_00126_19130805\oocihm.N_00126_19130805.5.txt</t>
         </is>
       </c>
       <c r="E222" s="1" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>42</t>
         </is>
       </c>
       <c r="F222" s="1" t="inlineStr">
@@ -29460,7 +29460,7 @@
       </c>
       <c r="G222" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H222" s="1" t="inlineStr">
@@ -29582,12 +29582,12 @@
       </c>
       <c r="C223" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.N_00126_19130805\oocihm.N_00126_19130805.6.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.N_00126_19130805\oocihm.N_00126_19130805.6.txt</t>
         </is>
       </c>
       <c r="D223" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.N_00126_19130805\oocihm.N_00126_19130805.6.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.N_00126_19130805\oocihm.N_00126_19130805.6.txt</t>
         </is>
       </c>
       <c r="E223" s="1" t="inlineStr">
@@ -29724,12 +29724,12 @@
       </c>
       <c r="C224" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.N_00126_19130805\oocihm.N_00126_19130805.7.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.N_00126_19130805\oocihm.N_00126_19130805.7.txt</t>
         </is>
       </c>
       <c r="D224" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.N_00126_19130805\oocihm.N_00126_19130805.7.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.N_00126_19130805\oocihm.N_00126_19130805.7.txt</t>
         </is>
       </c>
       <c r="E224" s="1" t="inlineStr">
@@ -29866,12 +29866,12 @@
       </c>
       <c r="C225" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.N_00126_19130805\oocihm.N_00126_19130805.8.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.N_00126_19130805\oocihm.N_00126_19130805.8.txt</t>
         </is>
       </c>
       <c r="D225" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.N_00126_19130805\oocihm.N_00126_19130805.8.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.N_00126_19130805\oocihm.N_00126_19130805.8.txt</t>
         </is>
       </c>
       <c r="E225" s="1" t="inlineStr">
@@ -30008,12 +30008,12 @@
       </c>
       <c r="C226" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.N_00138_18940629\oocihm.N_00138_18940629.1.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.N_00138_18940629\oocihm.N_00138_18940629.1.txt</t>
         </is>
       </c>
       <c r="D226" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.N_00138_18940629\oocihm.N_00138_18940629.1.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.N_00138_18940629\oocihm.N_00138_18940629.1.txt</t>
         </is>
       </c>
       <c r="E226" s="1" t="inlineStr">
@@ -30150,12 +30150,12 @@
       </c>
       <c r="C227" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.N_00138_18940629\oocihm.N_00138_18940629.2.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.N_00138_18940629\oocihm.N_00138_18940629.2.txt</t>
         </is>
       </c>
       <c r="D227" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.N_00138_18940629\oocihm.N_00138_18940629.2.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.N_00138_18940629\oocihm.N_00138_18940629.2.txt</t>
         </is>
       </c>
       <c r="E227" s="1" t="inlineStr">
@@ -30292,17 +30292,17 @@
       </c>
       <c r="C228" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.N_00138_18940629\oocihm.N_00138_18940629.3.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.N_00138_18940629\oocihm.N_00138_18940629.3.txt</t>
         </is>
       </c>
       <c r="D228" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.N_00138_18940629\oocihm.N_00138_18940629.3.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.N_00138_18940629\oocihm.N_00138_18940629.3.txt</t>
         </is>
       </c>
       <c r="E228" s="1" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>59</t>
         </is>
       </c>
       <c r="F228" s="1" t="inlineStr">
@@ -30312,7 +30312,7 @@
       </c>
       <c r="G228" s="1" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H228" s="1" t="inlineStr">
@@ -30434,12 +30434,12 @@
       </c>
       <c r="C229" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.N_00138_18940629\oocihm.N_00138_18940629.4.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.N_00138_18940629\oocihm.N_00138_18940629.4.txt</t>
         </is>
       </c>
       <c r="D229" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.N_00138_18940629\oocihm.N_00138_18940629.4.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.N_00138_18940629\oocihm.N_00138_18940629.4.txt</t>
         </is>
       </c>
       <c r="E229" s="1" t="inlineStr">
@@ -30576,12 +30576,12 @@
       </c>
       <c r="C230" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.N_00138_18940629\oocihm.N_00138_18940629.5.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.N_00138_18940629\oocihm.N_00138_18940629.5.txt</t>
         </is>
       </c>
       <c r="D230" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.N_00138_18940629\oocihm.N_00138_18940629.5.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.N_00138_18940629\oocihm.N_00138_18940629.5.txt</t>
         </is>
       </c>
       <c r="E230" s="1" t="inlineStr">
@@ -30718,12 +30718,12 @@
       </c>
       <c r="C231" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.N_00138_18940629\oocihm.N_00138_18940629.6.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.N_00138_18940629\oocihm.N_00138_18940629.6.txt</t>
         </is>
       </c>
       <c r="D231" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.N_00138_18940629\oocihm.N_00138_18940629.6.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.N_00138_18940629\oocihm.N_00138_18940629.6.txt</t>
         </is>
       </c>
       <c r="E231" s="1" t="inlineStr">
@@ -30860,12 +30860,12 @@
       </c>
       <c r="C232" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.N_00138_18940629\oocihm.N_00138_18940629.7.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.N_00138_18940629\oocihm.N_00138_18940629.7.txt</t>
         </is>
       </c>
       <c r="D232" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.N_00138_18940629\oocihm.N_00138_18940629.7.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.N_00138_18940629\oocihm.N_00138_18940629.7.txt</t>
         </is>
       </c>
       <c r="E232" s="1" t="inlineStr">
@@ -31002,12 +31002,12 @@
       </c>
       <c r="C233" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.N_00138_18940629\oocihm.N_00138_18940629.8.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.N_00138_18940629\oocihm.N_00138_18940629.8.txt</t>
         </is>
       </c>
       <c r="D233" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.N_00138_18940629\oocihm.N_00138_18940629.8.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.N_00138_18940629\oocihm.N_00138_18940629.8.txt</t>
         </is>
       </c>
       <c r="E233" s="1" t="inlineStr">
@@ -31144,12 +31144,12 @@
       </c>
       <c r="C234" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.N_00155_18750610\oocihm.N_00155_18750610.1.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.N_00155_18750610\oocihm.N_00155_18750610.1.txt</t>
         </is>
       </c>
       <c r="D234" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.N_00155_18750610\oocihm.N_00155_18750610.1.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.N_00155_18750610\oocihm.N_00155_18750610.1.txt</t>
         </is>
       </c>
       <c r="E234" s="1" t="inlineStr">
@@ -31286,12 +31286,12 @@
       </c>
       <c r="C235" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.N_00155_18750610\oocihm.N_00155_18750610.2.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.N_00155_18750610\oocihm.N_00155_18750610.2.txt</t>
         </is>
       </c>
       <c r="D235" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.N_00155_18750610\oocihm.N_00155_18750610.2.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.N_00155_18750610\oocihm.N_00155_18750610.2.txt</t>
         </is>
       </c>
       <c r="E235" s="1" t="inlineStr">
@@ -31428,17 +31428,17 @@
       </c>
       <c r="C236" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.N_00155_18750610\oocihm.N_00155_18750610.3.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.N_00155_18750610\oocihm.N_00155_18750610.3.txt</t>
         </is>
       </c>
       <c r="D236" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.N_00155_18750610\oocihm.N_00155_18750610.3.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.N_00155_18750610\oocihm.N_00155_18750610.3.txt</t>
         </is>
       </c>
       <c r="E236" s="1" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>119</t>
         </is>
       </c>
       <c r="F236" s="1" t="inlineStr">
@@ -31448,7 +31448,7 @@
       </c>
       <c r="G236" s="1" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H236" s="1" t="inlineStr">
@@ -31570,12 +31570,12 @@
       </c>
       <c r="C237" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.N_00155_18750610\oocihm.N_00155_18750610.4.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.N_00155_18750610\oocihm.N_00155_18750610.4.txt</t>
         </is>
       </c>
       <c r="D237" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.N_00155_18750610\oocihm.N_00155_18750610.4.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.N_00155_18750610\oocihm.N_00155_18750610.4.txt</t>
         </is>
       </c>
       <c r="E237" s="1" t="inlineStr">
@@ -31590,7 +31590,7 @@
       </c>
       <c r="G237" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H237" s="1" t="inlineStr">
@@ -31712,12 +31712,12 @@
       </c>
       <c r="C238" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.N_00155_18880712\oocihm.N_00155_18880712.1.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.N_00155_18880712\oocihm.N_00155_18880712.1.txt</t>
         </is>
       </c>
       <c r="D238" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.N_00155_18880712\oocihm.N_00155_18880712.1.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.N_00155_18880712\oocihm.N_00155_18880712.1.txt</t>
         </is>
       </c>
       <c r="E238" s="1" t="inlineStr">
@@ -31854,12 +31854,12 @@
       </c>
       <c r="C239" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.N_00155_18880712\oocihm.N_00155_18880712.2.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.N_00155_18880712\oocihm.N_00155_18880712.2.txt</t>
         </is>
       </c>
       <c r="D239" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.N_00155_18880712\oocihm.N_00155_18880712.2.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.N_00155_18880712\oocihm.N_00155_18880712.2.txt</t>
         </is>
       </c>
       <c r="E239" s="1" t="inlineStr">
@@ -31996,12 +31996,12 @@
       </c>
       <c r="C240" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.N_00155_18880712\oocihm.N_00155_18880712.3.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.N_00155_18880712\oocihm.N_00155_18880712.3.txt</t>
         </is>
       </c>
       <c r="D240" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.N_00155_18880712\oocihm.N_00155_18880712.3.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.N_00155_18880712\oocihm.N_00155_18880712.3.txt</t>
         </is>
       </c>
       <c r="E240" s="1" t="inlineStr">
@@ -32138,12 +32138,12 @@
       </c>
       <c r="C241" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.N_00155_18880712\oocihm.N_00155_18880712.4.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.N_00155_18880712\oocihm.N_00155_18880712.4.txt</t>
         </is>
       </c>
       <c r="D241" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.N_00155_18880712\oocihm.N_00155_18880712.4.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.N_00155_18880712\oocihm.N_00155_18880712.4.txt</t>
         </is>
       </c>
       <c r="E241" s="1" t="inlineStr">
@@ -32280,12 +32280,12 @@
       </c>
       <c r="C242" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.N_00155_18880712\oocihm.N_00155_18880712.5.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.N_00155_18880712\oocihm.N_00155_18880712.5.txt</t>
         </is>
       </c>
       <c r="D242" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.N_00155_18880712\oocihm.N_00155_18880712.5.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.N_00155_18880712\oocihm.N_00155_18880712.5.txt</t>
         </is>
       </c>
       <c r="E242" s="1" t="inlineStr">
@@ -32422,12 +32422,12 @@
       </c>
       <c r="C243" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.N_00155_18880712\oocihm.N_00155_18880712.6.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.N_00155_18880712\oocihm.N_00155_18880712.6.txt</t>
         </is>
       </c>
       <c r="D243" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.N_00155_18880712\oocihm.N_00155_18880712.6.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.N_00155_18880712\oocihm.N_00155_18880712.6.txt</t>
         </is>
       </c>
       <c r="E243" s="1" t="inlineStr">
@@ -32564,12 +32564,12 @@
       </c>
       <c r="C244" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.N_00155_18880712\oocihm.N_00155_18880712.7.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.N_00155_18880712\oocihm.N_00155_18880712.7.txt</t>
         </is>
       </c>
       <c r="D244" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.N_00155_18880712\oocihm.N_00155_18880712.7.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.N_00155_18880712\oocihm.N_00155_18880712.7.txt</t>
         </is>
       </c>
       <c r="E244" s="1" t="inlineStr">
@@ -32706,12 +32706,12 @@
       </c>
       <c r="C245" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.N_00155_18880712\oocihm.N_00155_18880712.8.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.N_00155_18880712\oocihm.N_00155_18880712.8.txt</t>
         </is>
       </c>
       <c r="D245" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.N_00155_18880712\oocihm.N_00155_18880712.8.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.N_00155_18880712\oocihm.N_00155_18880712.8.txt</t>
         </is>
       </c>
       <c r="E245" s="1" t="inlineStr">
@@ -32848,12 +32848,12 @@
       </c>
       <c r="C246" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.N_00219_18600707\oocihm.N_00219_18600707.1.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.N_00219_18600707\oocihm.N_00219_18600707.1.txt</t>
         </is>
       </c>
       <c r="D246" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.N_00219_18600707\oocihm.N_00219_18600707.1.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.N_00219_18600707\oocihm.N_00219_18600707.1.txt</t>
         </is>
       </c>
       <c r="E246" s="1" t="inlineStr">
@@ -32990,12 +32990,12 @@
       </c>
       <c r="C247" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.N_00219_18600707\oocihm.N_00219_18600707.2.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.N_00219_18600707\oocihm.N_00219_18600707.2.txt</t>
         </is>
       </c>
       <c r="D247" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.N_00219_18600707\oocihm.N_00219_18600707.2.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.N_00219_18600707\oocihm.N_00219_18600707.2.txt</t>
         </is>
       </c>
       <c r="E247" s="1" t="inlineStr">
@@ -33132,12 +33132,12 @@
       </c>
       <c r="C248" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.N_00219_18600707\oocihm.N_00219_18600707.3.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.N_00219_18600707\oocihm.N_00219_18600707.3.txt</t>
         </is>
       </c>
       <c r="D248" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.N_00219_18600707\oocihm.N_00219_18600707.3.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.N_00219_18600707\oocihm.N_00219_18600707.3.txt</t>
         </is>
       </c>
       <c r="E248" s="1" t="inlineStr">
@@ -33274,12 +33274,12 @@
       </c>
       <c r="C249" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.N_00219_18600707\oocihm.N_00219_18600707.4.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.N_00219_18600707\oocihm.N_00219_18600707.4.txt</t>
         </is>
       </c>
       <c r="D249" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.N_00219_18600707\oocihm.N_00219_18600707.4.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.N_00219_18600707\oocihm.N_00219_18600707.4.txt</t>
         </is>
       </c>
       <c r="E249" s="1" t="inlineStr">
